--- a/data/processed/harmonization/Carbon__Total_carbon/10.5061_DRYAD.0K6DJHB5K/10.5061_DRYAD.0K6DJHB5K_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.5061_DRYAD.0K6DJHB5K/10.5061_DRYAD.0K6DJHB5K_soil_Carbon__Total_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>320.560 Ridge 0-10 HF:0-10</t>
+          <t>320.560 Ridge 0-10 HF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>320.560 Ridge 10-35 HF:10-35</t>
+          <t>320.560 Ridge 10-35 HF:Ridge:10-35</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>320.560 Ridge 35-60 HF:35-60</t>
+          <t>320.560 Ridge 35-60 HF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>360.600 Ridge 0-10 HF:0-10</t>
+          <t>360.600 Ridge 0-10 HF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>360.600 Ridge 35-60 HF:35-60</t>
+          <t>360.600 Ridge 35-60 HF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>360.680 Ridge 0-10 HF:0-10</t>
+          <t>360.680 Ridge 0-10 HF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>360.680 Ridge 10-35 HF:10-35</t>
+          <t>360.680 Ridge 10-35 HF:Ridge:10-35</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>360.680 Ridge 35-60 HF:35-60</t>
+          <t>360.680 Ridge 35-60 HF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>120.520 R. V. 0-10 HF:0-10</t>
+          <t>120.520 R. V. 0-10 HF:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>120.520 R.V. 10-25 HF:10-25</t>
+          <t>120.520 R.V. 10-25 HF:Riparian Valley:10-25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>160.680 R.V. 0-10 HF:0-10</t>
+          <t>160.680 R.V. 0-10 HF:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>160.680 R. V. 10-35 HF:10-35</t>
+          <t>160.680 R. V. 10-35 HF:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>160.680 R. V. 35-60 HF:35-60</t>
+          <t>160.680 R. V. 35-60 HF:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>280.560 Slope 0-10 HF:0-10</t>
+          <t>280.560 Slope 0-10 HF:Slope:0-10</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>280.560 Slope 10-35 HF:10-35</t>
+          <t>280.560 Slope 10-35 HF:Slope:10-35</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>280.560 Slope 35-60 HF:35-60</t>
+          <t>280.560 Slope 35-60 HF:Slope:35-60</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>360.720 Slope 0-10 HF:0-10</t>
+          <t>360.720 Slope 0-10 HF:Slope:0-10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>360.720 Slope 10-35 HF:10-35</t>
+          <t>360.720 Slope 10-35 HF:Slope:10-35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>360.720 Slope 35-60 HF:35-60</t>
+          <t>360.720 Slope 35-60 HF:Slope:35-60</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80.520 slope 0-10 HF:0-10</t>
+          <t>80.520 slope 0-10 HF:Slope:0-10</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>80.520 slope 10-35 HF:10-35</t>
+          <t>80.520 slope 10-35 HF:Slope:10-35</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>80.520 slope 35-60 HF-redo:35-60</t>
+          <t>80.520 slope 35-60 HF-redo:Slope:35-60</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>200.600 Valley U 0-10 HF:0-10</t>
+          <t>200.600 Valley U 0-10 HF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>200.600 Valley U 10-35 HF:10-35</t>
+          <t>200.600 Valley U 10-35 HF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>200.600 Valley U 35-60 HF:35-60</t>
+          <t>200.600 Valley U 35-60 HF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>280.720 Valley U 0-10 HF:0-10</t>
+          <t>280.720 Valley U 0-10 HF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>280.720 Valley U 10-35 HF:10-35</t>
+          <t>280.720 Valley U 10-35 HF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>280.720.Valley U 35-60 HF:35-60</t>
+          <t>280.720.Valley U 35-60 HF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>320.520 Valley U 0-10 HF:0-10</t>
+          <t>320.520 Valley U 0-10 HF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>320.520 Valley U 10-35 HF:10-35</t>
+          <t>320.520 Valley U 10-35 HF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>320.520 Valley U 35-60 HF:35-60</t>
+          <t>320.520 Valley U 35-60 HF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>320_560 Ridge 0_10 OLF:0-10</t>
+          <t>320_560 Ridge 0_10 OLF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>320_560 Ridge 10_35 OLF:10-35</t>
+          <t>320_560 Ridge 10_35 OLF:Ridge:10-35</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>320_560 Ridge 35_60 OLF:35-60</t>
+          <t>320_560 Ridge 35_60 OLF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>360_600 Ridge 0_10 OLF:0-10</t>
+          <t>360_600 Ridge 0_10 OLF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>360_600 Ridge 35_60 OLF:35-60</t>
+          <t>360_600 Ridge 35_60 OLF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>360_680 Ridge 0-10 OLF:0-10</t>
+          <t>360_680 Ridge 0-10 OLF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>360_680 Ridge 10_35 OLF:10-35</t>
+          <t>360_680 Ridge 10_35 OLF:Ridge:10-35</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>360_680 Ridge 35_60 OLF:35-60</t>
+          <t>360_680 Ridge 35_60 OLF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>120_520 RV 0_10 OLF:0-10</t>
+          <t>120_520 RV 0_10 OLF:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>120_520 RV 10_25 OLF:10-25</t>
+          <t>120_520 RV 10_25 OLF:Riparian Valley:10-25</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>160_680 RV 0_10 OLF:0-10</t>
+          <t>160_680 RV 0_10 OLF:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>160_680 RV 10_35 OLF:10-35</t>
+          <t>160_680 RV 10_35 OLF:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>160_680 RV 35_60 OLF:35-60</t>
+          <t>160_680 RV 35_60 OLF:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>280_560 Slope 0-10 OLF:0-10</t>
+          <t>280_560 Slope 0-10 OLF:Slope:0-10</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>280_560 Slope 10-35 OLF:10-35</t>
+          <t>280_560 Slope 10-35 OLF:Slope:10-35</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>280_560 Slope 35-60 OLF:35-60</t>
+          <t>280_560 Slope 35-60 OLF:Slope:35-60</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>360_720 Slope 0-10 OLF:0-10</t>
+          <t>360_720 Slope 0-10 OLF:Slope:0-10</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>360_720 Slope 10-35 OLF:10-35</t>
+          <t>360_720 Slope 10-35 OLF:Slope:10-35</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>360_720 Slope 35-60 OLF:35-60</t>
+          <t>360_720 Slope 35-60 OLF:Slope:35-60</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>80_520 Slope 0-10 OLF:0-10</t>
+          <t>80_520 Slope 0-10 OLF:Slope:0-10</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>80_520 Slope 10_35 OLF:10-35</t>
+          <t>80_520 Slope 10_35 OLF:Slope:10-35</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>80_520 Slope 35_60 OLF_DT:35-60</t>
+          <t>80_520 Slope 35_60 OLF_DT:Slope:35-60</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>200_600_ Valley U 0_10 OLF:0-10</t>
+          <t>200_600_ Valley U 0_10 OLF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>200_600 Valley U 10_35 OLF:10-35</t>
+          <t>200_600 Valley U 10_35 OLF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>200_600 Valley U 35_60 OLF:35-60</t>
+          <t>200_600 Valley U 35_60 OLF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>280_720 Valley U 0_10 OLF:0-10</t>
+          <t>280_720 Valley U 0_10 OLF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>280_720 Valley U 10_35 OLF:10-35</t>
+          <t>280_720 Valley U 10_35 OLF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>280_720 Valley U 35_60 OLF:35-60</t>
+          <t>280_720 Valley U 35_60 OLF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>320_520 Valley U 0-10 OLF:0-10</t>
+          <t>320_520 Valley U 0-10 OLF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>320_520 Valley U 10_35 OLF:10-35</t>
+          <t>320_520 Valley U 10_35 OLF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>320_520 Valley U 35_60 OLF:35-60</t>
+          <t>320_520 Valley U 35_60 OLF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>320.560 Ridge 0-10:0-10</t>
+          <t>320.560 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>320.560 Ridge 10-35_DT:10-35</t>
+          <t>320.560 Ridge 10-35_DT:Ridge:10-35</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>320.560 Ridge 35-60:35-60</t>
+          <t>320.560 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>360.600 Ridge 0-10:0-10</t>
+          <t>360.600 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>360.600 Ridge 35-60 DT:35-60</t>
+          <t>360.600 Ridge 35-60 DT:Ridge:35-60</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>360.680 Ridge 0-10:0-10</t>
+          <t>360.680 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>360.680 Ridge 10-35 QAQC:10-35</t>
+          <t>360.680 Ridge 10-35 QAQC:Ridge:10-35</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>360.680 Ridge 35-60:35-60</t>
+          <t>360.680 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>120.520 R.V 0-10:0-10</t>
+          <t>120.520 R.V 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>120.520 R.V 10-25:10-25</t>
+          <t>120.520 R.V 10-25:Riparian Valley:10-25</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>160.680 R.V 0-10:0-10</t>
+          <t>160.680 R.V 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4539,12 +4539,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>160.680 R.V 10-35:10-35</t>
+          <t>160.680 R.V 10-35:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>160.680 R.V 35-60:35-60</t>
+          <t>160.680 R.V 35-60:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>280.560 Slope 0-10:0-10</t>
+          <t>280.560 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>280.560 Slope 10-35:10-35</t>
+          <t>280.560 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>280.560 Slope 35-60:35-60</t>
+          <t>280.560 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>360.720 Slope 0-10:0-10</t>
+          <t>360.720 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>360.720 Slope 10-35:10-35</t>
+          <t>360.720 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>360.720 Slope 35-60:35-60</t>
+          <t>360.720 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>80.520 Slope 0-10:0-10</t>
+          <t>80.520 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>80.520 Slope 10-35 QAQC:10-35</t>
+          <t>80.520 Slope 10-35 QAQC:Slope:10-35</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>80.520 Slope 35-60:35-60</t>
+          <t>80.520 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>200.600 Valley V 0-10 QAQC:0-10</t>
+          <t>200.600 Valley V 0-10 QAQC:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>200.600 Valley V 10-35:10-35</t>
+          <t>200.600 Valley V 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>200.600 Valley V 35-60 DT:35-60</t>
+          <t>200.600 Valley V 35-60 DT:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>280.720 Valley U 0-10:0-10</t>
+          <t>280.720 Valley U 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>280.720 Valley U 10-35:10-35</t>
+          <t>280.720 Valley U 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>280.720 Valleu U 35-60_DT:35-60</t>
+          <t>280.720 Valleu U 35-60_DT:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>320.520 Valley V 0-10:0-10</t>
+          <t>320.520 Valley V 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>320.520 Valley U 10-35:10-35</t>
+          <t>320.520 Valley U 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>320.520 Valley U 35-60:35-60</t>
+          <t>320.520 Valley U 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>360_680 Ridge 0-10  FLF:0-10</t>
+          <t>360_680 Ridge 0-10  FLF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>360_680 Ridge 10-35 FLF:10-35</t>
+          <t>360_680 Ridge 10-35 FLF:Ridge:10-35</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>360_680 Ridge 35-60 FLF:35-60</t>
+          <t>360_680 Ridge 35-60 FLF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>360_600 Ridge 0-10 FLF:0-10</t>
+          <t>360_600 Ridge 0-10 FLF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>360_600 Ridge 35-60 FLF:35-60</t>
+          <t>360_600 Ridge 35-60 FLF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>320_560 Ridge 0-10 FLF:0-10</t>
+          <t>320_560 Ridge 0-10 FLF:Ridge:0-10</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>320_560 Ridge 10-35 FLF:10-35</t>
+          <t>320_560 Ridge 10-35 FLF:Ridge:10-35</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>320_560 Ridge 35-60 FLF:35-60</t>
+          <t>320_560 Ridge 35-60 FLF:Ridge:35-60</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>120_520 RV 0_10 FLF:0-10</t>
+          <t>120_520 RV 0_10 FLF:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>120_520 RV 10_25 FLF:10-25</t>
+          <t>120_520 RV 10_25 FLF:Riparian Valley:10-25</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>160_680 R. Valley 0-10 FLF:0-10</t>
+          <t>160_680 R. Valley 0-10 FLF:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>160_680 R. Valley 10-35 FLF:10-35</t>
+          <t>160_680 R. Valley 10-35 FLF:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>160_680 RV 35_60 FLF:35-60</t>
+          <t>160_680 RV 35_60 FLF:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>280_560 Slope 0-10 FLF DT:0-10</t>
+          <t>280_560 Slope 0-10 FLF DT:Slope:0-10</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>280_560 Slope 10-35 FLF:10-35</t>
+          <t>280_560 Slope 10-35 FLF:Slope:10-35</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>280_560 Slope 35-60 FLF:35-60</t>
+          <t>280_560 Slope 35-60 FLF:Slope:35-60</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>360_720 Slope 0-10 FLF:0-10</t>
+          <t>360_720 Slope 0-10 FLF:Slope:0-10</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>360_720 Slope 10-35 FLF:10-35</t>
+          <t>360_720 Slope 10-35 FLF:Slope:10-35</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>360_720 Slope 35-60 FLF:35-60</t>
+          <t>360_720 Slope 35-60 FLF:Slope:35-60</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>80_520 Slope 0-10 FLF:0-10</t>
+          <t>80_520 Slope 0-10 FLF:Slope:0-10</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>80_520 Slope 10_35 FLF:10-35</t>
+          <t>80_520 Slope 10_35 FLF:Slope:10-35</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>80_520 Slope 35_60 OLF:35-60</t>
+          <t>80_520 Slope 35_60 OLF:Slope:35-60</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>200_600 Valley U 0_10 FLF:0-10</t>
+          <t>200_600 Valley U 0_10 FLF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>200_600 Valley U 10_35 FLF:10-35</t>
+          <t>200_600 Valley U 10_35 FLF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>200_600 Valley U 35-50 FLF:35-60</t>
+          <t>200_600 Valley U 35-50 FLF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>280_720 Valley U 0-10 FLF:0-10</t>
+          <t>280_720 Valley U 0-10 FLF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>280_720 Valley U 10-35 FLF:10-35</t>
+          <t>280_720 Valley U 10-35 FLF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>280_720 Valley U 35-60 FLF:35-60</t>
+          <t>280_720 Valley U 35-60 FLF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>320_520 Valley U 0-10 FLF:0-10</t>
+          <t>320_520 Valley U 0-10 FLF:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>320_520 Valley U 10-35 FLF:10-35</t>
+          <t>320_520 Valley U 10-35 FLF:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>320_520 Valley U 35-60 FLF:35-60</t>
+          <t>320_520 Valley U 35-60 FLF:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 0-10:0-10</t>
+          <t>360, 520 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 10-35:10-35</t>
+          <t>360, 520 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 35-60:35-60</t>
+          <t>360, 520 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 0-10:0-10</t>
+          <t>280, 440 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 10-35:10-35</t>
+          <t>280, 440 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 35-60:35-60</t>
+          <t>280, 440 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 0-10:0-10</t>
+          <t>280, 480 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 10-35:10-35</t>
+          <t>280, 480 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 35-60:35-60</t>
+          <t>280, 480 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 0-10:0-10</t>
+          <t>200, 560 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 10-35:10-35</t>
+          <t>200, 560 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 35-60:35-60</t>
+          <t>200, 560 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 0-10:0-10</t>
+          <t>240, 440 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 10-35:10-35</t>
+          <t>240, 440 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 35-60:35-60</t>
+          <t>240, 440 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 0-10:0-10</t>
+          <t>80, 520 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 10-35:10-35</t>
+          <t>80, 520 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 35-60:35-60</t>
+          <t>80, 520 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 0-10:0-10</t>
+          <t>200, 600 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 10-35:10-35</t>
+          <t>200, 600 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 35-60:35-60</t>
+          <t>200, 600 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 0-10:0-10</t>
+          <t>220, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 10-35:10-35</t>
+          <t>220, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 35-60:35-60</t>
+          <t>220, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 0-10:0-10</t>
+          <t>160, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 10-35:10-35</t>
+          <t>160, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 35-60:35-60</t>
+          <t>160, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 0-10:0-10</t>
+          <t>120, 520 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 10-25:10-35</t>
+          <t>120, 520 R. Valley 10-25:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 0-10:0-10</t>
+          <t>120, 560 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 10-35:10-35</t>
+          <t>120, 560 R. Valley 10-35:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -9049,12 +9049,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 35-60:35-60</t>
+          <t>120, 560 R. Valley 35-60:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 0-10:0-10</t>
+          <t>360, 520 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 10-35:10-35</t>
+          <t>360, 520 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 35-60:35-60</t>
+          <t>360, 520 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 0-10:0-10</t>
+          <t>280, 440 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 10-35:10-35</t>
+          <t>280, 440 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 35-60:35-60</t>
+          <t>280, 440 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 0-10:0-10</t>
+          <t>280, 480 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -9489,12 +9489,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 10-35:10-35</t>
+          <t>280, 480 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 35-60:35-60</t>
+          <t>280, 480 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 0-10:0-10</t>
+          <t>200, 560 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 10-35:10-35</t>
+          <t>200, 560 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 0-10:0-10</t>
+          <t>240, 440 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 10-35:10-35</t>
+          <t>240, 440 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 35-60:35-60</t>
+          <t>240, 440 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 0-10:0-10</t>
+          <t>80, 520 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 10-35:10-35</t>
+          <t>80, 520 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 35-60:35-60</t>
+          <t>80, 520 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 0-10:0-10</t>
+          <t>200, 600 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 10-35:10-35</t>
+          <t>200, 600 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -10149,12 +10149,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 35-60:35-60</t>
+          <t>200, 600 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 0-10:0-10</t>
+          <t>220, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 10-35:10-35</t>
+          <t>220, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 35-60:35-60</t>
+          <t>220, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 0-10:0-10</t>
+          <t>160, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -10424,12 +10424,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 10-35:10-35</t>
+          <t>160, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 35-60:35-60</t>
+          <t>160, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 0-10:0-10</t>
+          <t>120, 520 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 10-25:10-35</t>
+          <t>120, 520 R. Valley 10-25:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 0-10:0-10</t>
+          <t>120, 560 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 10-35:10-35</t>
+          <t>120, 560 R. Valley 10-35:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 35-60:35-60</t>
+          <t>120, 560 R. Valley 35-60:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 0-10:0-10</t>
+          <t>360, 520 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 10-35:10-35</t>
+          <t>360, 520 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 35-60:35-60</t>
+          <t>360, 520 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 0-10:0-10</t>
+          <t>280, 440 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -11029,12 +11029,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 10-35:10-35</t>
+          <t>280, 440 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 35-60:35-60</t>
+          <t>280, 440 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 0-10:0-10</t>
+          <t>280, 480 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 10-35:10-35</t>
+          <t>280, 480 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 35-60:35-60</t>
+          <t>280, 480 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 0-10:0-10</t>
+          <t>200, 560 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 10-35:10-35</t>
+          <t>200, 560 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -11414,12 +11414,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 35-60:35-60</t>
+          <t>200, 560 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 0-10:0-10</t>
+          <t>240, 440 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 10-35:10-35</t>
+          <t>240, 440 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 35-60:35-60</t>
+          <t>240, 440 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11634,12 +11634,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 0-10:0-10</t>
+          <t>80, 520 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 10-35:10-35</t>
+          <t>80, 520 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 35-60:35-60</t>
+          <t>80, 520 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 0-10:0-10</t>
+          <t>200, 600 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 10-35:10-35</t>
+          <t>200, 600 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 35-60:35-60</t>
+          <t>200, 600 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 0-10:0-10</t>
+          <t>220, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 10-35:10-35</t>
+          <t>220, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 35-60:35-60</t>
+          <t>220, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 0-10:0-10</t>
+          <t>160, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 10-35:10-35</t>
+          <t>160, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 35-60:35-60</t>
+          <t>160, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -12294,12 +12294,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 0-10:0-10</t>
+          <t>120, 520 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -12349,12 +12349,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 10-25:10-35</t>
+          <t>120, 520 R. Valley 10-25:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 0-10:0-10</t>
+          <t>120, 560 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 10-35:10-35</t>
+          <t>120, 560 R. Valley 10-35:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 35-60:35-60</t>
+          <t>120, 560 R. Valley 35-60:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 0-10:0-10</t>
+          <t>360, 520 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -12624,12 +12624,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 10-35:10-35</t>
+          <t>360, 520 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12679,12 +12679,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>360, 520 Ridge 35-60:35-60</t>
+          <t>360, 520 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 0-10:0-10</t>
+          <t>280, 440 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 10-35:10-35</t>
+          <t>280, 440 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>280, 440 Ridge 35-60:35-60</t>
+          <t>280, 440 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 0-10:0-10</t>
+          <t>280, 480 Ridge 0-10:Ridge:0-10</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 10-35:10-35</t>
+          <t>280, 480 Ridge 10-35:Ridge:10-35</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>280, 480 Ridge 35-60:35-60</t>
+          <t>280, 480 Ridge 35-60:Ridge:35-60</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 0-10:0-10</t>
+          <t>200, 560 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 10-35:10-35</t>
+          <t>200, 560 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>200, 560 Slope 35-60:35-60</t>
+          <t>200, 560 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 0-10:0-10</t>
+          <t>240, 440 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 10-35:10-35</t>
+          <t>240, 440 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -13339,12 +13339,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>240, 440 Slope 35-60:35-60</t>
+          <t>240, 440 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 0-10:0-10</t>
+          <t>80, 520 Slope 0-10:Slope:0-10</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 10-35:10-35</t>
+          <t>80, 520 Slope 10-35:Slope:10-35</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -13504,12 +13504,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>80, 520 Slope 35-60:35-60</t>
+          <t>80, 520 Slope 35-60:Slope:35-60</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 0-10:0-10</t>
+          <t>200, 600 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 10-35:10-35</t>
+          <t>200, 600 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>200, 600 Valley 35-60:35-60</t>
+          <t>200, 600 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 0-10:0-10</t>
+          <t>220, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 10-35:10-35</t>
+          <t>220, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>220, 560 Valley 35-60:35-60</t>
+          <t>220, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 0-10:0-10</t>
+          <t>160, 560 Valley 0-10:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 10-35:10-35</t>
+          <t>160, 560 Valley 10-35:Upland Valley:10-35</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>160, 560 Valley 35-60:35-60</t>
+          <t>160, 560 Valley 35-60:Upland Valley:35-60</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -14054,12 +14054,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 0-10:0-10</t>
+          <t>120, 520 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -14109,12 +14109,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>120, 520 R. Valley 10-25:10-35</t>
+          <t>120, 520 R. Valley 10-25:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -14164,12 +14164,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 0-10:0-10</t>
+          <t>120, 560 R. Valley 0-10:Riparian Valley:0-10</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 10-35:10-35</t>
+          <t>120, 560 R. Valley 10-35:Riparian Valley:10-35</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -14274,12 +14274,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>120, 560 R. Valley 35-60:35-60</t>
+          <t>120, 560 R. Valley 35-60:Riparian Valley:35-60</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -14329,12 +14329,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Upland Valley:10-20</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -14494,12 +14494,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Upland Valley:10-20</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -14549,12 +14549,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Upland Valley:10-20</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -14604,12 +14604,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -14659,12 +14659,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Upland Valley:10-20</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Upland Valley:0-10</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -14769,12 +14769,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Upland Valley:10-20</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Slope:0-10</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Slope:10-20</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14934,12 +14934,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Slope:0-10</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Slope:10-20</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -15044,12 +15044,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Slope:0-10</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -15099,12 +15099,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Slope:10-20</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -15154,12 +15154,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Slope:0-10</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -15209,12 +15209,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Slope:10-20</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Slope:0-10</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Slope:10-20</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Ridge:0-10</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Ridge:10-20</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Ridge:0-10</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -15539,12 +15539,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Ridge:10-20</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -15594,12 +15594,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Ridge:0-10</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -15649,12 +15649,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Ridge:10-20</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Ridge:0-10</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -15759,12 +15759,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Ridge:10-20</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:0-10</t>
+          <t>Hall et al 2015:Ridge:0-10</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -15869,12 +15869,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Hall et al 2015:10-20</t>
+          <t>Hall et al 2015:Ridge:10-20</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Sample:depth</t>
+          <t>Sample:Topography:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
